--- a/data/trans_orig/IBSE_100-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IBSE_100-Provincia-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>74,53</t>
+          <t>74,3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>71,49</t>
+          <t>71,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73,06</t>
+          <t>72,98</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,3; 76,15</t>
+          <t>73,26; 75,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,64; 72,25</t>
+          <t>70,88; 72,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,22; 73,95</t>
+          <t>72,32; 73,6</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82,9</t>
+          <t>82,8</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78,97</t>
+          <t>79,09</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80,94</t>
+          <t>80,92</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,23; 84,48</t>
+          <t>81,1; 84,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,56; 80,05</t>
+          <t>77,88; 80,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,86; 81,94</t>
+          <t>79,94; 81,94</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80,76</t>
+          <t>80,37</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76,12</t>
+          <t>75,85</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78,35</t>
+          <t>77,99</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,51; 82,79</t>
+          <t>78,28; 82,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74,11; 77,89</t>
+          <t>73,97; 77,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,96; 79,71</t>
+          <t>76,7; 79,38</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>83,84</t>
+          <t>84,63</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,55</t>
+          <t>79,25</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,25</t>
+          <t>81,78</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,95; 86,47</t>
+          <t>82,26; 86,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,51; 81,61</t>
+          <t>77,13; 81,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,58; 82,81</t>
+          <t>79,93; 83,34</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68,59</t>
+          <t>68,75</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64,53</t>
+          <t>64,74</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66,4</t>
+          <t>66,64</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,63; 70,65</t>
+          <t>66,91; 70,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,94; 65,96</t>
+          <t>63,31; 66,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,18; 67,7</t>
+          <t>65,46; 67,93</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>78,03</t>
+          <t>77,34</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75,96</t>
+          <t>75,69</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77,02</t>
+          <t>76,52</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75,7; 80,12</t>
+          <t>75,13; 79,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,81; 77,92</t>
+          <t>73,37; 77,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,42; 78,65</t>
+          <t>74,84; 78,06</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>79,44</t>
+          <t>79,64</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>76,83</t>
+          <t>75,71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77,93</t>
+          <t>77,61</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,8; 80,82</t>
+          <t>78,15; 80,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,87; 79,09</t>
+          <t>74,35; 77,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76,81; 79,26</t>
+          <t>76,65; 78,56</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77,25</t>
+          <t>73,64</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68,58</t>
+          <t>68,67</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73,47</t>
+          <t>71,1</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>72,94; 82,97</t>
+          <t>72,18; 75,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>67,28; 69,83</t>
+          <t>67,33; 70,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70,64; 79,97</t>
+          <t>70,04; 71,98</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>78,74</t>
+          <t>78,01</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74,56</t>
+          <t>73,98</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76,6</t>
+          <t>75,94</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>77,71; 80,8</t>
+          <t>77,33; 78,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,81; 75,62</t>
+          <t>73,45; 74,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75,91; 78,06</t>
+          <t>75,47; 76,37</t>
         </is>
       </c>
     </row>
